--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -494,6 +494,9 @@
     <t>Whether the event actually happened, or just had the potential to. Note that this is independent of whether anyone was affected or harmed or how severely.</t>
   </si>
   <si>
+    <t>actual</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -501,6 +504,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/adverse-event-actuality|4.0.1</t>
+  </si>
+  <si>
+    <t>1877-1: fixed value = #actual</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -546,6 +552,9 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-type</t>
   </si>
   <si>
+    <t>1905: source value from ADERS - 18_VAE_Desc</t>
+  </si>
+  <si>
     <t>FiveWs.what[x]</t>
   </si>
   <si>
@@ -610,6 +619,9 @@
     <t>The date (and perhaps time) when the adverse event occurred.</t>
   </si>
   <si>
+    <t>1881: transform using concat(4_VacDate, 4_VacTime)</t>
+  </si>
+  <si>
     <t>FiveWs.init</t>
   </si>
   <si>
@@ -706,6 +718,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>1919: source value from ADERS - 21_NOA</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -2551,7 +2566,7 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>88</v>
@@ -2578,7 +2593,7 @@
         <v>80</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>80</v>
@@ -2593,13 +2608,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -2632,13 +2647,13 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -2646,10 +2661,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2672,13 +2687,13 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2705,13 +2720,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -2729,7 +2744,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2750,7 +2765,7 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -2758,10 +2773,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2775,7 +2790,7 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -2784,13 +2799,13 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2817,13 +2832,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -2841,7 +2856,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2856,13 +2871,13 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -2870,14 +2885,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2896,19 +2911,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -2957,7 +2972,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -2972,13 +2987,13 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -2986,10 +3001,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3012,16 +3027,16 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3071,7 +3086,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3092,7 +3107,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -3100,10 +3115,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3117,7 +3132,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -3126,13 +3141,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3183,7 +3198,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3198,13 +3213,13 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3212,10 +3227,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3238,13 +3253,13 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3295,7 +3310,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3324,10 +3339,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3350,16 +3365,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3409,7 +3424,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3430,7 +3445,7 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3438,10 +3453,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3464,13 +3479,13 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3521,7 +3536,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3550,10 +3565,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3576,13 +3591,13 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3633,7 +3648,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3662,10 +3677,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3688,13 +3703,13 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3721,31 +3736,31 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Z22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3774,10 +3789,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3800,13 +3815,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3833,31 +3848,31 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3886,10 +3901,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3903,7 +3918,7 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -3912,13 +3927,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3945,31 +3960,31 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Z24" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3984,7 +3999,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -3998,10 +4013,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4024,13 +4039,13 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4081,7 +4096,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4102,7 +4117,7 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4110,10 +4125,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4136,13 +4151,13 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4193,7 +4208,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4222,10 +4237,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4248,13 +4263,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4305,7 +4320,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4334,10 +4349,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4360,13 +4375,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4417,7 +4432,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4441,15 +4456,15 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4478,7 +4493,7 @@
         <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>136</v>
@@ -4531,7 +4546,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4555,19 +4570,19 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4589,10 +4604,10 @@
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>136</v>
@@ -4647,7 +4662,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4676,14 +4691,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4702,13 +4717,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4759,7 +4774,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>87</v>
@@ -4788,10 +4803,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4814,13 +4829,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4871,7 +4886,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4900,10 +4915,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4926,13 +4941,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4983,7 +4998,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5007,15 +5022,15 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5044,7 +5059,7 @@
         <v>134</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>136</v>
@@ -5097,7 +5112,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5121,19 +5136,19 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5155,10 +5170,10 @@
         <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>136</v>
@@ -5213,7 +5228,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5242,10 +5257,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5268,13 +5283,13 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5301,13 +5316,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5325,7 +5340,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5354,10 +5369,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5380,13 +5395,13 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5437,7 +5452,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5466,10 +5481,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5492,13 +5507,13 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5549,7 +5564,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5578,10 +5593,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5604,13 +5619,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5637,13 +5652,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -5661,7 +5676,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5690,10 +5705,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5716,13 +5731,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5773,7 +5788,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5802,10 +5817,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5828,13 +5843,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5885,7 +5900,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5914,10 +5929,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5940,13 +5955,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5997,7 +6012,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="292">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to AdverseEvent</t>
+    <t>This StructureDefinition contains the maps for ADERS to AdverseEvent</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -552,7 +552,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-type</t>
   </si>
   <si>
-    <t>1905: source value from ADERS - 18_VAE_Desc</t>
+    <t>1905: source value from ADERS - 18_VAE_Desc (A-18)</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -581,7 +581,7 @@
     <t>Allows for exposure of biohazard (such as legionella) to a group of individuals in a hospital.</t>
   </si>
   <si>
-    <t>1877: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1877: reference from ADERS - 0_Pt_ICN_Full (A-0)</t>
   </si>
   <si>
     <t>FiveWs.who</t>
@@ -619,7 +619,7 @@
     <t>The date (and perhaps time) when the adverse event occurred.</t>
   </si>
   <si>
-    <t>1881: transform using concat(4_VacDate, 4_VacTime)</t>
+    <t>1881: transform using concat(4_VacDate, 4_VacTime) on ADERS - (A-)</t>
   </si>
   <si>
     <t>FiveWs.init</t>
@@ -720,7 +720,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
   </si>
   <si>
-    <t>1919: source value from ADERS - 21_NOA</t>
+    <t>1919: source value from ADERS - 21_NOA (A-21.9)</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Immunization|Procedure|Substance|Medication|MedicationAdministration|MedicationStatement|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac1)
 </t>
   </si>
   <si>
@@ -825,6 +825,9 @@
   </si>
   <si>
     <t>Identifies the actual instance of what caused the adverse event.  May be a substance, medication, medication administration, medication statement or a device.</t>
+  </si>
+  <si>
+    <t>1972: reference</t>
   </si>
   <si>
     <t>AdverseEvent.suspectEntity.causality</t>
@@ -1279,7 +1282,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="24.98046875" customWidth="true" bestFit="true"/>
@@ -4708,7 +4711,7 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
@@ -4789,7 +4792,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
@@ -4803,10 +4806,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4832,10 +4835,10 @@
         <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4886,7 +4889,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4915,10 +4918,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5027,10 +5030,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5141,10 +5144,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5257,10 +5260,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5286,10 +5289,10 @@
         <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5319,10 +5322,10 @@
         <v>169</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5340,7 +5343,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5369,10 +5372,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5398,10 +5401,10 @@
         <v>241</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5452,7 +5455,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5481,10 +5484,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5507,13 +5510,13 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5564,7 +5567,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5593,10 +5596,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5622,10 +5625,10 @@
         <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5655,10 +5658,10 @@
         <v>169</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -5676,7 +5679,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5705,10 +5708,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5731,13 +5734,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5788,7 +5791,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5817,10 +5820,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5843,13 +5846,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5900,7 +5903,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5929,10 +5932,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5955,13 +5958,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6012,7 +6015,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,7 +552,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-type</t>
   </si>
   <si>
-    <t>1905: source value from ADERS - 18_VAE_Desc (A-18)</t>
+    <t>1905: source value from ADERS - VAE_Desc (A-18)</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -581,7 +581,7 @@
     <t>Allows for exposure of biohazard (such as legionella) to a group of individuals in a hospital.</t>
   </si>
   <si>
-    <t>1877: reference from ADERS - 0_Pt_ICN_Full (A-0)</t>
+    <t>1877: reference from ADERS - Pt_ICN_Full (A-0)</t>
   </si>
   <si>
     <t>FiveWs.who</t>
@@ -720,7 +720,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
   </si>
   <si>
-    <t>1919: source value from ADERS - 21_NOA (A-21.9)</t>
+    <t>1919: source value from ADERS - NOA (A-21.9)</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,7 +552,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-type</t>
   </si>
   <si>
-    <t>1905: source value from ADERS - VAE_Desc (A-18)</t>
+    <t>1905: source value from ADERS - 18_VAE_Desc</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -581,7 +581,7 @@
     <t>Allows for exposure of biohazard (such as legionella) to a group of individuals in a hospital.</t>
   </si>
   <si>
-    <t>1877: reference from ADERS - Pt_ICN_Full (A-0)</t>
+    <t>1877: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>FiveWs.who</t>
@@ -619,7 +619,7 @@
     <t>The date (and perhaps time) when the adverse event occurred.</t>
   </si>
   <si>
-    <t>1881: transform using concat(4_VacDate, 4_VacTime) on ADERS - (A-)</t>
+    <t>1881: transform using concat(4_VacDate, 4_VacTime)</t>
   </si>
   <si>
     <t>FiveWs.init</t>
@@ -720,7 +720,7 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
   </si>
   <si>
-    <t>1919: source value from ADERS - NOA (A-21.9)</t>
+    <t>1919: source value from ADERS - 21_NOA</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac1)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSImmunizationvac1)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="340">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,10 +552,94 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-type</t>
   </si>
   <si>
-    <t>1905: source value from ADERS - 18_VAE_Desc</t>
-  </si>
-  <si>
     <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>AdverseEvent.event.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AdverseEvent.event.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.event.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>1905: transform using parseText()</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>AdverseEvent.event.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>AdverseEvent.subject</t>
@@ -720,7 +804,92 @@
     <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome|4.0.1</t>
   </si>
   <si>
+    <t>AdverseEvent.outcome.id</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome1</t>
+  </si>
+  <si>
+    <t>va-outcome1</t>
+  </si>
+  <si>
+    <t>1906: source value from ADERS - 21_VAE_Outcome_DrVisit</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome2</t>
+  </si>
+  <si>
+    <t>va-outcome2</t>
+  </si>
+  <si>
+    <t>1907: source value from ADERS - 21_VAE_Outcome_ErED</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome3</t>
+  </si>
+  <si>
+    <t>va-outcome3</t>
+  </si>
+  <si>
+    <t>1908: source value from ADERS - 21_HospStay</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome8</t>
+  </si>
+  <si>
+    <t>va-outcome8</t>
+  </si>
+  <si>
+    <t>1913: source value from ADERS - 21_ProlongHospStay</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome9</t>
+  </si>
+  <si>
+    <t>va-outcome9</t>
+  </si>
+  <si>
+    <t>1914: source value from ADERS - 21_LTI</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome10</t>
+  </si>
+  <si>
+    <t>va-outcome10</t>
+  </si>
+  <si>
+    <t>1915: source value from ADERS - 21_Dis</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome11</t>
+  </si>
+  <si>
+    <t>va-outcome11</t>
+  </si>
+  <si>
+    <t>1918: source value from ADERS - 21_CA_BD</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome12</t>
+  </si>
+  <si>
+    <t>va-outcome12</t>
+  </si>
+  <si>
     <t>1919: source value from ADERS - 21_NOA</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.text</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -768,29 +937,7 @@
     <t>AdverseEvent.suspectEntity.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AdverseEvent.suspectEntity.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AdverseEvent.suspectEntity.modifierExtension</t>
@@ -1244,12 +1391,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.48828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.48828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.29296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1275,7 +1422,7 @@
     <col min="26" max="26" width="56.046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="54.48828125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1285,7 +1432,7 @@
     <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="46.53125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2793,7 +2940,7 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -2874,13 +3021,13 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -2888,46 +3035,42 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2975,10 +3118,10 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>87</v>
@@ -2987,38 +3130,38 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3027,19 +3170,19 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3077,31 +3220,31 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -3110,18 +3253,18 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3132,7 +3275,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>88</v>
@@ -3144,16 +3287,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3201,13 +3348,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3216,24 +3363,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3256,16 +3403,20 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3313,7 +3464,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3337,29 +3488,29 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -3368,18 +3519,20 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -3427,10 +3580,10 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>87</v>
@@ -3442,13 +3595,13 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3456,10 +3609,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3470,7 +3623,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -3482,15 +3635,17 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3539,13 +3694,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -3560,7 +3715,7 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -3568,10 +3723,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3585,7 +3740,7 @@
         <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -3594,13 +3749,13 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3651,7 +3806,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3666,13 +3821,13 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
@@ -3680,10 +3835,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3706,13 +3861,13 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3739,13 +3894,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -3763,7 +3918,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3792,10 +3947,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3818,15 +3973,17 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -3851,13 +4008,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>219</v>
+        <v>80</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -3875,7 +4032,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3896,7 +4053,7 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -3904,10 +4061,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3918,10 +4075,10 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -3930,13 +4087,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3963,13 +4120,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -3987,13 +4144,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4002,7 +4159,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -4016,10 +4173,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4042,13 +4199,13 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4099,7 +4256,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4120,7 +4277,7 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4128,10 +4285,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4142,7 +4299,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4154,13 +4311,13 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4187,13 +4344,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4211,13 +4368,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -4240,10 +4397,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4254,7 +4411,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4266,13 +4423,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4299,13 +4456,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -4323,13 +4480,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -4352,10 +4509,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4375,16 +4532,16 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4411,13 +4568,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -4435,7 +4592,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4447,7 +4604,7 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -4459,26 +4616,26 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -4490,17 +4647,15 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4549,19 +4704,19 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -4573,19 +4728,19 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>245</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4598,26 +4753,24 @@
         <v>80</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>134</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O30" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4653,19 +4806,19 @@
         <v>80</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4689,29 +4842,29 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>130</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
@@ -4720,16 +4873,20 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>256</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -4765,25 +4922,23 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -4792,7 +4947,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
@@ -4801,17 +4956,19 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>80</v>
       </c>
@@ -4820,10 +4977,10 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
@@ -4832,16 +4989,20 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>187</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -4889,7 +5050,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4904,7 +5065,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -4913,17 +5074,19 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
       </c>
@@ -4935,25 +5098,29 @@
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5001,22 +5168,22 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5025,49 +5192,53 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>245</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5115,7 +5286,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5127,10 +5298,10 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5139,50 +5310,52 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>245</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5231,7 +5404,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5243,10 +5416,10 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5255,17 +5428,19 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>130</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5277,7 +5452,7 @@
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5286,16 +5461,20 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>267</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5319,13 +5498,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5343,13 +5522,13 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>266</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
@@ -5358,7 +5537,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -5367,17 +5546,19 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5389,7 +5570,7 @@
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>80</v>
@@ -5398,16 +5579,20 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>272</v>
+        <v>187</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5455,13 +5640,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>271</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -5470,7 +5655,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -5479,17 +5664,19 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5501,7 +5688,7 @@
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
@@ -5510,16 +5697,20 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>187</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5567,13 +5758,13 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
@@ -5582,7 +5773,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
@@ -5591,7 +5782,7 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -5599,9 +5790,11 @@
         <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -5613,7 +5806,7 @@
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
@@ -5622,16 +5815,20 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>279</v>
+        <v>187</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -5655,13 +5852,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -5679,13 +5876,13 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
@@ -5694,7 +5891,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>80</v>
@@ -5703,15 +5900,15 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5722,7 +5919,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -5734,16 +5931,20 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -5791,13 +5992,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>199</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -5815,15 +6016,15 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5834,7 +6035,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -5846,13 +6047,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5903,13 +6104,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -5924,7 +6125,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -5932,10 +6133,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5958,13 +6159,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>289</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6015,7 +6216,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6042,8 +6243,1812 @@
         <v>80</v>
       </c>
     </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN42">
+  <autoFilter ref="A1:AN58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6053,7 +8058,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI41">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -615,7 +615,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1905: transform using parseText()</t>
+    <t>1905: transform using parseCodesFromText()</t>
   </si>
   <si>
     <t>union(., ./translation)</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="339">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
@@ -1391,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.48828125" customWidth="true" bestFit="true"/>
@@ -1430,9 +1427,8 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1553,9 +1549,6 @@
       <c r="AM1" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="AN1" t="s" s="1">
-        <v>76</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1566,6489 +1559,6318 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>122</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>142</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="P11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G12" t="s" s="2">
+      <c r="I12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="T12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X12" t="s" s="2">
+      <c r="Y12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AA12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="AA13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AF16" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K18" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H19" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G19" t="s" s="2">
+      <c r="I19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="P19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH24" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="AA26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="AA27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AA28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AC30" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AC30" t="s" s="2">
+      <c r="AD30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE30" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AD30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE30" t="s" s="2">
+      <c r="AF30" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AF30" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="AG30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH30" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH31" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O32" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O33" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O34" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="B35" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="D35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H35" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O35" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH35" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O36" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="B37" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O37" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH37" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH38" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H39" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="P39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="P40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K41" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="M45" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH45" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G46" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH46" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G47" t="s" s="2">
+      <c r="I47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH48" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G50" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH50" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH51" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH51" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AA52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K55" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AA55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G56" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G56" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH56" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G57" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH57" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G58" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH58" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN58">
+  <autoFilter ref="A1:AM58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to AdverseEvent</t>
+    <t>This StructureDefinition contains the maps for ADERS to AdverseEvent.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -866,6 +866,15 @@
   </si>
   <si>
     <t>1915: source value from ADERS - 21_Dis</t>
+  </si>
+  <si>
+    <t>AdverseEvent.outcome.coding:va-outcome-13</t>
+  </si>
+  <si>
+    <t>va-outcome-13</t>
+  </si>
+  <si>
+    <t>1916: source value from ADERS - 21_Death</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome11</t>
@@ -1388,12 +1397,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.48828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.48828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.29296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5787,9 +5796,11 @@
         <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>79</v>
       </c>
@@ -5801,7 +5812,7 @@
         <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>79</v>
@@ -5810,19 +5821,19 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -5871,13 +5882,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -5886,21 +5897,21 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5923,16 +5934,20 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>282</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -5980,7 +5995,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5998,18 +6013,18 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6020,7 +6035,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6032,13 +6047,13 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6089,13 +6104,13 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
@@ -6107,7 +6122,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6115,10 +6130,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6141,13 +6156,13 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6198,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6224,10 +6239,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6238,7 +6253,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6247,16 +6262,16 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>174</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>175</v>
+        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6307,19 +6322,19 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>176</v>
+        <v>293</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -6328,26 +6343,26 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -6359,17 +6374,15 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6418,19 +6431,19 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -6444,14 +6457,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6464,26 +6477,24 @@
         <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -6531,7 +6542,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6552,47 +6563,51 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I47" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>303</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -6640,50 +6655,50 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
@@ -6692,13 +6707,13 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6749,13 +6764,13 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
@@ -6764,7 +6779,7 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
@@ -6789,7 +6804,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -6798,16 +6813,16 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>174</v>
+        <v>311</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6858,19 +6873,19 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>176</v>
+        <v>310</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -6879,26 +6894,26 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -6910,17 +6925,15 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -6969,19 +6982,19 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -6995,14 +7008,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7015,26 +7028,24 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="O51" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7082,7 +7093,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7103,47 +7114,51 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -7167,13 +7182,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7191,19 +7206,19 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -7212,15 +7227,15 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7243,13 +7258,13 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7276,13 +7291,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7300,7 +7315,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7352,13 +7367,13 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7435,10 +7450,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7461,7 +7476,7 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>159</v>
+        <v>325</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>326</v>
@@ -7494,13 +7509,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -7518,7 +7533,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7544,10 +7559,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7558,7 +7573,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -7570,13 +7585,13 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>331</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7603,13 +7618,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -7627,13 +7642,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -7869,8 +7884,117 @@
         <v>79</v>
       </c>
     </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM58">
+  <autoFilter ref="A1:AM59">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7880,7 +8004,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI57">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -810,7 +810,7 @@
     <t>AdverseEvent.outcome.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -868,10 +868,10 @@
     <t>1915: source value from ADERS - 21_Dis</t>
   </si>
   <si>
-    <t>AdverseEvent.outcome.coding:va-outcome-13</t>
-  </si>
-  <si>
-    <t>va-outcome-13</t>
+    <t>AdverseEvent.outcome.coding:va-outcome13</t>
+  </si>
+  <si>
+    <t>va-outcome13</t>
   </si>
   <si>
     <t>1916: source value from ADERS - 21_Death</t>
@@ -1402,7 +1402,7 @@
   <cols>
     <col min="1" max="1" width="54.48828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.48828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.29296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -662,7 +662,7 @@
     <t>Allows for exposure of biohazard (such as legionella) to a group of individuals in a hospital.</t>
   </si>
   <si>
-    <t>1877: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1877: reference based on ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>FiveWs.who</t>
@@ -820,7 +820,7 @@
     <t>va-outcome1</t>
   </si>
   <si>
-    <t>1906: source value from ADERS - 21_VAE_Outcome_DrVisit</t>
+    <t>1906: source value based on ADERS - 21_VAE_Outcome_DrVisit</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome2</t>
@@ -829,7 +829,7 @@
     <t>va-outcome2</t>
   </si>
   <si>
-    <t>1907: source value from ADERS - 21_VAE_Outcome_ErED</t>
+    <t>1907: source value based on ADERS - 21_VAE_Outcome_ErED</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome3</t>
@@ -838,7 +838,7 @@
     <t>va-outcome3</t>
   </si>
   <si>
-    <t>1908: source value from ADERS - 21_HospStay</t>
+    <t>1908: source value based on ADERS - 21_HospStay</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome8</t>
@@ -847,7 +847,7 @@
     <t>va-outcome8</t>
   </si>
   <si>
-    <t>1913: source value from ADERS - 21_ProlongHospStay</t>
+    <t>1913: source value based on ADERS - 21_ProlongHospStay</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome9</t>
@@ -856,7 +856,7 @@
     <t>va-outcome9</t>
   </si>
   <si>
-    <t>1914: source value from ADERS - 21_LTI</t>
+    <t>1914: source value based on ADERS - 21_LTI</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome10</t>
@@ -865,7 +865,7 @@
     <t>va-outcome10</t>
   </si>
   <si>
-    <t>1915: source value from ADERS - 21_Dis</t>
+    <t>1915: source value based on ADERS - 21_Dis</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome13</t>
@@ -874,7 +874,7 @@
     <t>va-outcome13</t>
   </si>
   <si>
-    <t>1916: source value from ADERS - 21_Death</t>
+    <t>1916: source value based on ADERS - 21_Death</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome11</t>
@@ -883,7 +883,7 @@
     <t>va-outcome11</t>
   </si>
   <si>
-    <t>1918: source value from ADERS - 21_CA_BD</t>
+    <t>1918: source value based on ADERS - 21_CA_BD</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome12</t>
@@ -892,7 +892,7 @@
     <t>va-outcome12</t>
   </si>
   <si>
-    <t>1919: source value from ADERS - 21_NOA</t>
+    <t>1919: source value based on ADERS - 21_NOA</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.text</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,6 +636,9 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>2217: source value based on ADERS - 18_VAE_Desc</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -820,7 +823,11 @@
     <t>va-outcome1</t>
   </si>
   <si>
-    <t>1906: source value based on ADERS - 21_VAE_Outcome_DrVisit</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1906:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" {null}</t>
+  </si>
+  <si>
+    <t>1906: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome2</t>
@@ -829,7 +836,11 @@
     <t>va-outcome2</t>
   </si>
   <si>
-    <t>1907: source value based on ADERS - 21_VAE_Outcome_ErED</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1907:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" {null}</t>
+  </si>
+  <si>
+    <t>1907: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome3</t>
@@ -838,7 +849,11 @@
     <t>va-outcome3</t>
   </si>
   <si>
-    <t>1908: source value based on ADERS - 21_HospStay</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1908:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+  </si>
+  <si>
+    <t>1908: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome8</t>
@@ -847,7 +862,11 @@
     <t>va-outcome8</t>
   </si>
   <si>
-    <t>1913: source value based on ADERS - 21_ProlongHospStay</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1913:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+  </si>
+  <si>
+    <t>1913: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome9</t>
@@ -856,7 +875,11 @@
     <t>va-outcome9</t>
   </si>
   <si>
-    <t>1914: source value based on ADERS - 21_LTI</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1914:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" {null}</t>
+  </si>
+  <si>
+    <t>1914: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome10</t>
@@ -865,7 +888,11 @@
     <t>va-outcome10</t>
   </si>
   <si>
-    <t>1915: source value based on ADERS - 21_Dis</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1915:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" {null}</t>
+  </si>
+  <si>
+    <t>1915: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome13</t>
@@ -874,7 +901,11 @@
     <t>va-outcome13</t>
   </si>
   <si>
-    <t>1916: source value based on ADERS - 21_Death</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1916:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" {null}</t>
+  </si>
+  <si>
+    <t>1916: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome11</t>
@@ -883,7 +914,11 @@
     <t>va-outcome11</t>
   </si>
   <si>
-    <t>1918: source value based on ADERS - 21_CA_BD</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1918:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" {null}</t>
+  </si>
+  <si>
+    <t>1918: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome12</t>
@@ -892,7 +927,11 @@
     <t>va-outcome12</t>
   </si>
   <si>
-    <t>1919: source value based on ADERS - 21_NOA</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersae-17-1919:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" {null}</t>
+  </si>
+  <si>
+    <t>1919: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.text</t>
@@ -1435,7 +1474,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="124.640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
   </cols>
@@ -3348,7 +3387,7 @@
         <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
@@ -3433,25 +3472,25 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3470,19 +3509,19 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3531,7 +3570,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>86</v>
@@ -3546,10 +3585,10 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -3557,10 +3596,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3583,16 +3622,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3642,7 +3681,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3660,7 +3699,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3668,10 +3707,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3694,13 +3733,13 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3751,7 +3790,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3766,10 +3805,10 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -3777,10 +3816,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3803,13 +3842,13 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3860,7 +3899,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3886,10 +3925,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3912,16 +3951,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3971,7 +4010,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3989,7 +4028,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -3997,10 +4036,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4023,13 +4062,13 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4080,7 +4119,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4106,10 +4145,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4132,13 +4171,13 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4189,7 +4228,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4215,10 +4254,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4244,10 +4283,10 @@
         <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4277,10 +4316,10 @@
         <v>168</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4298,7 +4337,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4324,10 +4363,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4353,10 +4392,10 @@
         <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4386,10 +4425,10 @@
         <v>153</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4407,7 +4446,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4433,10 +4472,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4462,10 +4501,10 @@
         <v>159</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4495,10 +4534,10 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4516,7 +4555,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4542,10 +4581,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4651,10 +4690,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4762,10 +4801,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4837,7 +4876,7 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4873,13 +4912,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -4974,10 +5013,10 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -4988,13 +5027,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -5089,10 +5128,10 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -5103,13 +5142,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -5204,10 +5243,10 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>267</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
@@ -5218,13 +5257,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -5319,10 +5358,10 @@
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>271</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5333,13 +5372,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -5434,10 +5473,10 @@
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -5448,13 +5487,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>79</v>
@@ -5549,10 +5588,10 @@
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5563,13 +5602,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -5664,10 +5703,10 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>283</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5678,13 +5717,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -5779,10 +5818,10 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>287</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -5793,13 +5832,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>79</v>
@@ -5894,10 +5933,10 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>291</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
@@ -5908,10 +5947,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6016,15 +6055,15 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6047,13 +6086,13 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6104,7 +6143,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6122,7 +6161,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6130,10 +6169,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6156,13 +6195,13 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6213,7 +6252,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6239,10 +6278,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6265,13 +6304,13 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6322,7 +6361,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6348,10 +6387,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6457,10 +6496,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6568,14 +6607,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6597,10 +6636,10 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>135</v>
@@ -6655,7 +6694,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6681,14 +6720,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6707,13 +6746,13 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6764,7 +6803,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>86</v>
@@ -6779,7 +6818,7 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
@@ -6790,10 +6829,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6816,13 +6855,13 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6873,7 +6912,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6899,10 +6938,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7008,10 +7047,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7119,14 +7158,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7148,10 +7187,10 @@
         <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7206,7 +7245,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7232,10 +7271,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7261,10 +7300,10 @@
         <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7294,10 +7333,10 @@
         <v>168</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7315,7 +7354,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7341,10 +7380,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7370,10 +7409,10 @@
         <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7424,7 +7463,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7450,10 +7489,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7476,13 +7515,13 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7533,7 +7572,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7559,10 +7598,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7588,10 +7627,10 @@
         <v>159</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7621,10 +7660,10 @@
         <v>168</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -7642,7 +7681,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7668,10 +7707,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7694,13 +7733,13 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7751,7 +7790,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7777,10 +7816,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7803,13 +7842,13 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7860,7 +7899,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7886,10 +7925,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7912,13 +7951,13 @@
         <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7969,7 +8008,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1905: transform using parseCodesFromText()</t>
+    <t>1905: transform using parseCodesFromText() on ADERS - 18_VAE_Desc (18)</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
@@ -636,7 +636,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>2217: source value based on ADERS - 18_VAE_Desc</t>
+    <t>2217: source value based on ADERS - 18_VAE_Desc (18)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -665,7 +665,7 @@
     <t>Allows for exposure of biohazard (such as legionella) to a group of individuals in a hospital.</t>
   </si>
   <si>
-    <t>1877: reference based on ADERS - 0_Pt_ICN_Full</t>
+    <t>1877: reference based on ADERS - 0_Pt_ICN_Full (0)</t>
   </si>
   <si>
     <t>FiveWs.who</t>
@@ -824,10 +824,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1906:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" {null}</t>
-  </si>
-  <si>
-    <t>1906: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" if =1</t>
+vaersae-17-1906:If (21-1) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" {null}</t>
+  </si>
+  <si>
+    <t>1906: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" when ADERS - 21_VAE_Outcome_DrVisit (21-1) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome2</t>
@@ -837,10 +837,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1907:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" {null}</t>
-  </si>
-  <si>
-    <t>1907: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" if =1</t>
+vaersae-17-1907:If (21-2) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" {null}</t>
+  </si>
+  <si>
+    <t>1907: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" when ADERS - 21_VAE_Outcome_ErED (21-2) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome3</t>
@@ -850,10 +850,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1908:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
-  </si>
-  <si>
-    <t>1908: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" if =1</t>
+vaersae-17-1908:If (21-3) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+  </si>
+  <si>
+    <t>1908: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" when ADERS - 21_HospStay (21-3) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome8</t>
@@ -863,10 +863,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1913:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
-  </si>
-  <si>
-    <t>1913: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" if =1</t>
+vaersae-17-1913:If (21-4) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+  </si>
+  <si>
+    <t>1913: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" when ADERS - 21_ProlongHospStay (21-4) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome9</t>
@@ -876,10 +876,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1914:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" {null}</t>
-  </si>
-  <si>
-    <t>1914: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" if =1</t>
+vaersae-17-1914:If (21-5) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" {null}</t>
+  </si>
+  <si>
+    <t>1914: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" when ADERS - 21_LTI (21-5) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome10</t>
@@ -889,10 +889,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1915:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" {null}</t>
-  </si>
-  <si>
-    <t>1915: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" if =1</t>
+vaersae-17-1915:If (21-6) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" {null}</t>
+  </si>
+  <si>
+    <t>1915: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" when ADERS - 21_Dis (21-6) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome13</t>
@@ -902,10 +902,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1916:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" {null}</t>
-  </si>
-  <si>
-    <t>1916: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" if =1</t>
+vaersae-17-1916:If (21-7) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" {null}</t>
+  </si>
+  <si>
+    <t>1916: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" when ADERS - 21_Death (21-7) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome11</t>
@@ -915,10 +915,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1918:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" {null}</t>
-  </si>
-  <si>
-    <t>1918: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" if =1</t>
+vaersae-17-1918:If (21-8) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" {null}</t>
+  </si>
+  <si>
+    <t>1918: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" when ADERS - 21_CA_BD (21-8) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.coding:va-outcome12</t>
@@ -928,10 +928,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1919:If (null) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" {null}</t>
-  </si>
-  <si>
-    <t>1919: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" if =1</t>
+vaersae-17-1919:If (21-9) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" {null}</t>
+  </si>
+  <si>
+    <t>1919: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" when ADERS - 21_NOA (21-9) if =1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome.text</t>
@@ -1474,7 +1474,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="124.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="154.390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
   </cols>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -824,7 +824,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1906:If (21-1) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" {null}</t>
+vaersae-17-1906:If (21-1) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" {true}</t>
   </si>
   <si>
     <t>1906: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#drvisit "Doctor" when ADERS - 21_VAE_Outcome_DrVisit (21-1) if =1</t>
@@ -837,7 +837,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1907:If (21-2) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" {null}</t>
+vaersae-17-1907:If (21-2) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" {true}</t>
   </si>
   <si>
     <t>1907: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ered "Emergency Room" when ADERS - 21_VAE_Outcome_ErED (21-2) if =1</t>
@@ -850,7 +850,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1908:If (21-3) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+vaersae-17-1908:If (21-3) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {true}</t>
   </si>
   <si>
     <t>1908: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" when ADERS - 21_HospStay (21-3) if =1</t>
@@ -863,7 +863,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1913:If (21-4) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {null}</t>
+vaersae-17-1913:If (21-4) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" {true}</t>
   </si>
   <si>
     <t>1913: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#hospitalization "Hospitalization" when ADERS - 21_ProlongHospStay (21-4) if =1</t>
@@ -876,7 +876,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1914:If (21-5) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" {null}</t>
+vaersae-17-1914:If (21-5) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" {true}</t>
   </si>
   <si>
     <t>1914: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#lti "Life threatening illness" when ADERS - 21_LTI (21-5) if =1</t>
@@ -889,7 +889,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1915:If (21-6) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" {null}</t>
+vaersae-17-1915:If (21-6) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" {true}</t>
   </si>
   <si>
     <t>1915: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#dis "Disability or permanent damage" when ADERS - 21_Dis (21-6) if =1</t>
@@ -902,7 +902,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1916:If (21-7) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" {null}</t>
+vaersae-17-1916:If (21-7) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" {true}</t>
   </si>
   <si>
     <t>1916: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#death "Death" when ADERS - 21_Death (21-7) if =1</t>
@@ -915,7 +915,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1918:If (21-8) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" {null}</t>
+vaersae-17-1918:If (21-8) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" {true}</t>
   </si>
   <si>
     <t>1918: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#ca_db "Congenital anomaly or birth defect" when ADERS - 21_CA_BD (21-8) if =1</t>
@@ -928,7 +928,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersae-17-1919:If (21-9) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" {null}</t>
+vaersae-17-1919:If (21-9) is =1 then fixed value https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" {true}</t>
   </si>
   <si>
     <t>1919: fixed value = https://www.vaers.hhs.gov/data/datasets.html/Patientoutcomes#noa "None of the above" when ADERS - 21_NOA (21-9) if =1</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSAdverseEvent.xlsx
+++ b/docs/StructureDefinition-VAERSAdverseEvent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
